--- a/banks/preset_bank_profile.xlsx
+++ b/banks/preset_bank_profile.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16920" windowHeight="8700"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16920" windowHeight="8700" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Patch Banks" sheetId="1" r:id="rId1"/>
+    <sheet name="Drum kits" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511" refMode="R1C1"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="171">
   <si>
     <t>CC#32</t>
     <phoneticPr fontId="1"/>
@@ -506,6 +507,169 @@
   </si>
   <si>
     <t>SCC Preset 2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Prog.chg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Drum kit name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>file name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pss680_opnb.drumkit.json</t>
+  </si>
+  <si>
+    <t>ALSA Preset 2OP set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate from alsa_drums.hwbank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ALSA Preset 4OP set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dock Armory GM set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADPCM-A GM set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MA-2 Preset 2OP set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate from DrumsBank.hwbank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MA-2 Basic 2OP set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate from BasicDrumBank.hwbank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MA-2 Luminous 2OP set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate from LuminousDrumBank.hwbank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MA-2 MicroComputer 2OP set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate from MicroComputerDrumBank.hwbank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MA-2 Digital 2OP set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate from DigitalDrumBank.hwbank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MA-2 Acid 2OP set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate from AcidDrumBank.hwbank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MA-2 Variant 2OP set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate from 07_DrumsBank.hwbank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL Built-in set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>opll_rhythm.drumkit.json</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL Built-in set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># pending</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADPCM-B GM set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pss680_opna.drumkit.json</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># Multiple device (pending)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># no hwbank file</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL4-AWM GM set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>YRW801 GM Standard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># no hwbank file</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>YRW801 GM Standard drum</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GM Standard Native AWM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PCM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADPCM-B PSS-680/PSR-38</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPNA Built-in set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate with similar to OPLL built-in</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -836,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.21875" bestFit="1" customWidth="1"/>
@@ -938,19 +1102,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" t="s">
-        <v>82</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -958,16 +1119,16 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
         <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -975,16 +1136,16 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -992,33 +1153,33 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1026,16 +1187,16 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
         <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1043,16 +1204,16 @@
         <v>26</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
         <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1060,16 +1221,16 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
         <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1077,16 +1238,16 @@
         <v>26</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
         <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1094,16 +1255,16 @@
         <v>26</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
         <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -1111,16 +1272,16 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" t="s">
         <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1128,33 +1289,33 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
         <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1162,16 +1323,16 @@
         <v>34</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1179,16 +1340,16 @@
         <v>34</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1196,16 +1357,16 @@
         <v>34</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1213,16 +1374,16 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -1230,16 +1391,16 @@
         <v>34</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1247,16 +1408,16 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -1264,16 +1425,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1281,16 +1442,16 @@
         <v>34</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -1298,16 +1459,16 @@
         <v>34</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -1315,16 +1476,16 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -1332,16 +1493,16 @@
         <v>34</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -1349,16 +1510,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1366,16 +1527,16 @@
         <v>34</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1383,16 +1544,16 @@
         <v>34</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1400,16 +1561,16 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1417,16 +1578,16 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
       </c>
       <c r="D35" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1434,16 +1595,16 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1451,16 +1612,16 @@
         <v>34</v>
       </c>
       <c r="B37">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1468,16 +1629,16 @@
         <v>34</v>
       </c>
       <c r="B38">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1485,16 +1646,16 @@
         <v>34</v>
       </c>
       <c r="B39">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" t="s">
         <v>112</v>
-      </c>
-      <c r="C39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1502,16 +1663,16 @@
         <v>34</v>
       </c>
       <c r="B40">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1519,16 +1680,16 @@
         <v>34</v>
       </c>
       <c r="B41">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E41" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1536,16 +1697,16 @@
         <v>34</v>
       </c>
       <c r="B42">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E42" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1553,16 +1714,16 @@
         <v>34</v>
       </c>
       <c r="B43">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -1570,16 +1731,16 @@
         <v>34</v>
       </c>
       <c r="B44">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E44" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1587,16 +1748,16 @@
         <v>34</v>
       </c>
       <c r="B45">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -1604,33 +1765,33 @@
         <v>34</v>
       </c>
       <c r="B46">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="E47" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -1638,16 +1799,16 @@
         <v>40</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D48" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E48" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -1655,33 +1816,33 @@
         <v>40</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E49" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -1689,16 +1850,16 @@
         <v>48</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="s">
         <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -1706,16 +1867,16 @@
         <v>48</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
         <v>64</v>
       </c>
       <c r="D52" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E52" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1723,16 +1884,16 @@
         <v>48</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
         <v>64</v>
       </c>
       <c r="D53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E53" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1740,16 +1901,16 @@
         <v>48</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" t="s">
         <v>64</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1757,13 +1918,13 @@
         <v>48</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55" t="s">
         <v>64</v>
       </c>
       <c r="D55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E55" t="s">
         <v>119</v>
@@ -1774,13 +1935,13 @@
         <v>48</v>
       </c>
       <c r="B56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" t="s">
         <v>64</v>
       </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E56" t="s">
         <v>119</v>
@@ -1791,13 +1952,13 @@
         <v>48</v>
       </c>
       <c r="B57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C57" t="s">
         <v>64</v>
       </c>
       <c r="D57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E57" t="s">
         <v>119</v>
@@ -1808,13 +1969,13 @@
         <v>48</v>
       </c>
       <c r="B58">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
         <v>64</v>
       </c>
       <c r="D58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E58" t="s">
         <v>119</v>
@@ -1825,33 +1986,33 @@
         <v>48</v>
       </c>
       <c r="B59">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C59" t="s">
         <v>64</v>
       </c>
       <c r="D59" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E59" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
+        <v>48</v>
+      </c>
+      <c r="B60">
+        <v>112</v>
+      </c>
+      <c r="C60" t="s">
         <v>64</v>
       </c>
-      <c r="B60">
-        <v>0</v>
-      </c>
-      <c r="C60" t="s">
-        <v>120</v>
-      </c>
       <c r="D60" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="E60" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -1859,16 +2020,16 @@
         <v>64</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D61" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E61" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -1876,16 +2037,16 @@
         <v>64</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
         <v>123</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E62" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -1893,16 +2054,284 @@
         <v>64</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63" t="s">
         <v>123</v>
       </c>
       <c r="D63" t="s">
+        <v>128</v>
+      </c>
+      <c r="E63" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D64" t="s">
         <v>129</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E64" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>81</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65" t="s">
+        <v>167</v>
+      </c>
+      <c r="D65" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>84</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66" t="s">
+        <v>162</v>
+      </c>
+      <c r="D66" t="s">
+        <v>163</v>
+      </c>
+      <c r="E66" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>84</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>162</v>
+      </c>
+      <c r="D67" t="s">
+        <v>165</v>
+      </c>
+      <c r="E67" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/banks/preset_bank_profile.xlsx
+++ b/banks/preset_bank_profile.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16920" windowHeight="8700" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16920" windowHeight="8700"/>
   </bookViews>
   <sheets>
     <sheet name="Patch Banks" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="174">
   <si>
     <t>CC#32</t>
     <phoneticPr fontId="1"/>
@@ -427,10 +427,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>OPLL ROM Patched</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;builtin&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -670,6 +666,22 @@
   </si>
   <si>
     <t># generate with similar to OPLL built-in</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL Built-In</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Built-In with performance</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># generate skeleton, role=builtin_swpatch_meta</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1000,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.21875" bestFit="1" customWidth="1"/>
@@ -1055,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1111,7 +1123,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1655,7 +1667,7 @@
         <v>48</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1805,10 +1817,10 @@
         <v>107</v>
       </c>
       <c r="D48" t="s">
+        <v>171</v>
+      </c>
+      <c r="E48" t="s">
         <v>108</v>
-      </c>
-      <c r="E48" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -1819,13 +1831,13 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
+        <v>109</v>
+      </c>
+      <c r="D49" t="s">
         <v>110</v>
       </c>
-      <c r="D49" t="s">
-        <v>111</v>
-      </c>
       <c r="E49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -1836,30 +1848,30 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50" t="s">
         <v>114</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>115</v>
-      </c>
-      <c r="E50" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="E51" t="s">
-        <v>65</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -1867,16 +1879,16 @@
         <v>48</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="s">
         <v>64</v>
       </c>
       <c r="D52" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1884,16 +1896,16 @@
         <v>48</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
         <v>64</v>
       </c>
       <c r="D53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E53" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1901,16 +1913,16 @@
         <v>48</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54" t="s">
         <v>64</v>
       </c>
       <c r="D54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E54" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1918,16 +1930,16 @@
         <v>48</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55" t="s">
         <v>64</v>
       </c>
       <c r="D55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -1935,16 +1947,16 @@
         <v>48</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
         <v>64</v>
       </c>
       <c r="D56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E56" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -1952,16 +1964,16 @@
         <v>48</v>
       </c>
       <c r="B57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57" t="s">
         <v>64</v>
       </c>
       <c r="D57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -1969,16 +1981,16 @@
         <v>48</v>
       </c>
       <c r="B58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C58" t="s">
         <v>64</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -1986,16 +1998,16 @@
         <v>48</v>
       </c>
       <c r="B59">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
         <v>64</v>
       </c>
       <c r="D59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E59" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -2003,33 +2015,33 @@
         <v>48</v>
       </c>
       <c r="B60">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
         <v>64</v>
       </c>
       <c r="D60" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E60" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
+        <v>48</v>
+      </c>
+      <c r="B61">
+        <v>112</v>
+      </c>
+      <c r="C61" t="s">
         <v>64</v>
       </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61" t="s">
-        <v>120</v>
-      </c>
       <c r="D61" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="E61" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -2037,16 +2049,16 @@
         <v>64</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D62" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E62" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -2054,16 +2066,16 @@
         <v>64</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" t="s">
+        <v>122</v>
+      </c>
+      <c r="D63" t="s">
         <v>123</v>
       </c>
-      <c r="D63" t="s">
-        <v>128</v>
-      </c>
       <c r="E63" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -2071,47 +2083,47 @@
         <v>64</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D64" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E64" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
+        <v>128</v>
+      </c>
+      <c r="E65" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D66" t="s">
-        <v>163</v>
-      </c>
-      <c r="E66" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -2119,16 +2131,33 @@
         <v>84</v>
       </c>
       <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67" t="s">
+        <v>161</v>
+      </c>
+      <c r="D67" t="s">
+        <v>162</v>
+      </c>
+      <c r="E67" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>84</v>
+      </c>
+      <c r="B68">
         <v>1</v>
       </c>
-      <c r="C67" t="s">
-        <v>162</v>
-      </c>
-      <c r="D67" t="s">
-        <v>165</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="C68" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" t="s">
         <v>164</v>
+      </c>
+      <c r="E68" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2149,13 +2178,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" t="s">
         <v>130</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>131</v>
-      </c>
-      <c r="C1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2163,10 +2192,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2174,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2185,10 +2214,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" t="s">
         <v>134</v>
-      </c>
-      <c r="C4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2196,10 +2225,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2207,10 +2236,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" t="s">
         <v>139</v>
-      </c>
-      <c r="C6" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2218,10 +2247,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" t="s">
         <v>141</v>
-      </c>
-      <c r="C7" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2229,10 +2258,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
         <v>143</v>
-      </c>
-      <c r="C8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2240,10 +2269,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
         <v>145</v>
-      </c>
-      <c r="C9" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2251,10 +2280,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" t="s">
         <v>147</v>
-      </c>
-      <c r="C10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2262,10 +2291,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" t="s">
         <v>149</v>
-      </c>
-      <c r="C11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2273,10 +2302,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" t="s">
         <v>151</v>
-      </c>
-      <c r="C12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2284,10 +2313,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" t="s">
         <v>169</v>
-      </c>
-      <c r="C13" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2295,10 +2324,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
         <v>153</v>
-      </c>
-      <c r="C14" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2306,10 +2335,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" t="s">
         <v>155</v>
-      </c>
-      <c r="C15" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2317,10 +2346,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" t="s">
         <v>157</v>
-      </c>
-      <c r="C16" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2328,10 +2357,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
